--- a/NURBS IDX30 PYTHON ANALYSIS/Redo_front_4_24_26/15gps/6mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Redo_front_4_24_26/15gps/6mps_analysis.xlsx
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>691.6160854647662</v>
+        <v>691.7518577299466</v>
       </c>
       <c r="X3">
         <v>0.242965882</v>
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="W5">
-        <v>24.23989849372954</v>
+        <v>24.2399728131819</v>
       </c>
       <c r="X5">
         <v>0.242941126</v>
@@ -1901,7 +1901,7 @@
         <v>686.0494225923716</v>
       </c>
       <c r="V17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17">
         <v>0.24289098</v>
